--- a/outputs/checking1.xlsx
+++ b/outputs/checking1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rdata\RLE_est\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E17E95C-3394-4720-9BA9-82E5DC29A5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8373C54A-4EA9-4020-9D3F-1339E8FFB0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CDCFF45E-A600-4F0D-A091-9EAB302F8197}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="110">
   <si>
     <t>full_ecosystem_type_name</t>
   </si>
@@ -95,9 +95,6 @@
     <t>A3_18</t>
   </si>
   <si>
-    <t>B1aii_18</t>
-  </si>
-  <si>
     <t>B3_18</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>A3_24</t>
   </si>
   <si>
-    <t>B1aii_24</t>
-  </si>
-  <si>
     <t>B3_24</t>
   </si>
   <si>
@@ -230,9 +224,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>was LC now VU due to habitat loss in EFZ rate</t>
-  </si>
-  <si>
     <t>stays EN</t>
   </si>
   <si>
@@ -263,9 +254,6 @@
     <t xml:space="preserve">NBA2018 </t>
   </si>
   <si>
-    <t>EN to CR but driven by B1aii so reconsider</t>
-  </si>
-  <si>
     <t>prp_pa18</t>
   </si>
   <si>
@@ -353,14 +341,23 @@
     <t>was EN now LC</t>
   </si>
   <si>
-    <t>stays VU (B1a CR but it goes far into moz and so shouldn’t trigger B)</t>
+    <t>B1aii_24 (NOT USED)</t>
+  </si>
+  <si>
+    <t>B1aii_18 (NOTUSED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stays VU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">was LC now VU due to rate of  habitat loss in EFZ </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,14 +515,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -545,8 +534,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -732,6 +750,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -894,7 +918,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -902,13 +926,17 @@
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -955,119 +983,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="52">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill>
@@ -1177,146 +1093,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1650,114 +1426,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC5B220E-F33B-4C09-97F7-8857C99DE0BA}">
-  <dimension ref="A1:AQ23"/>
+  <dimension ref="A1:AP47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
     <col min="22" max="24" width="12" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="29" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="35" width="7.42578125" customWidth="1"/>
-    <col min="41" max="41" width="11.5703125" customWidth="1"/>
+    <col min="30" max="30" width="7.42578125" customWidth="1"/>
+    <col min="31" max="32" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="7.42578125" customWidth="1"/>
+    <col min="37" max="38" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="56.28515625" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="I1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>98</v>
+      </c>
+      <c r="O1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T1" t="s">
         <v>100</v>
       </c>
-      <c r="J1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" t="s">
-        <v>103</v>
-      </c>
       <c r="U1" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="V1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE1" t="s">
         <v>23</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="AF1" t="s">
         <v>24</v>
@@ -1766,48 +1553,45 @@
         <v>25</v>
       </c>
       <c r="AH1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" t="s">
         <v>26</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>32</v>
       </c>
       <c r="AJ1" t="s">
         <v>27</v>
       </c>
       <c r="AK1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>29</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>30</v>
       </c>
       <c r="AN1" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP1" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
+      <c r="C2">
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>14402116.57</v>
       </c>
       <c r="E2">
         <v>14402116.57</v>
@@ -1816,129 +1600,126 @@
         <v>14402116.57</v>
       </c>
       <c r="G2">
-        <v>14402116.57</v>
+        <v>2761.228791</v>
       </c>
       <c r="H2">
-        <v>2761.228791</v>
+        <v>59.78628483</v>
       </c>
       <c r="I2">
-        <v>59.78628483</v>
+        <v>61.248958330000001</v>
       </c>
       <c r="J2">
-        <v>61.248958330000001</v>
+        <v>0.784213194</v>
       </c>
       <c r="K2">
         <v>0.784213194</v>
       </c>
       <c r="L2">
+        <v>0.72341105900000002</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O2" s="5">
         <v>0.784213194</v>
-      </c>
-      <c r="M2">
-        <v>0.72341105900000002</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" t="s">
-        <v>105</v>
       </c>
       <c r="P2" s="5">
         <v>0.784213194</v>
       </c>
       <c r="Q2" s="5">
-        <v>0.784213194</v>
-      </c>
-      <c r="R2" s="5">
         <v>0.369969353</v>
       </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
       <c r="S2" t="s">
+        <v>102</v>
+      </c>
+      <c r="T2">
+        <v>11622400</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0.87596365600000003</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0.87210903100000003</v>
+      </c>
+      <c r="W2" s="5">
+        <v>0.83783039599999998</v>
+      </c>
+      <c r="X2" s="5">
+        <v>0.82760875599999995</v>
+      </c>
+      <c r="Y2">
+        <v>17562.5</v>
+      </c>
+      <c r="Z2">
+        <v>8.6253045E-2</v>
+      </c>
+      <c r="AA2">
+        <v>15828.57143</v>
+      </c>
+      <c r="AB2">
+        <v>7.7737366000000002E-2</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T2" t="s">
-        <v>106</v>
-      </c>
-      <c r="U2">
-        <v>11622400</v>
-      </c>
-      <c r="V2" s="5">
-        <v>0.87596365600000003</v>
-      </c>
-      <c r="W2" s="5">
-        <v>0.87210903100000003</v>
-      </c>
-      <c r="X2" s="5">
-        <v>0.83783039599999998</v>
-      </c>
-      <c r="Y2" s="5">
-        <v>0.82760875599999995</v>
-      </c>
-      <c r="Z2">
-        <v>17562.5</v>
-      </c>
-      <c r="AA2">
-        <v>8.6253045E-2</v>
-      </c>
-      <c r="AB2">
-        <v>15828.57143</v>
-      </c>
-      <c r="AC2">
-        <v>7.7737366000000002E-2</v>
-      </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>38</v>
       </c>
-      <c r="AE2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
       <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>60068831.420000002</v>
       </c>
       <c r="E3">
         <v>60068831.420000002</v>
@@ -1947,16 +1728,16 @@
         <v>60068831.420000002</v>
       </c>
       <c r="G3">
-        <v>60068831.420000002</v>
+        <v>71.288769090000002</v>
       </c>
       <c r="H3">
-        <v>71.288769090000002</v>
+        <v>84.625</v>
       </c>
       <c r="I3">
         <v>84.625</v>
       </c>
       <c r="J3">
-        <v>84.625</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -1964,112 +1745,109 @@
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>0</v>
+      <c r="M3" t="s">
+        <v>39</v>
       </c>
       <c r="N3" t="s">
+        <v>103</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T3">
+        <v>21792000</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0.98087371499999998</v>
+      </c>
+      <c r="V3" s="5">
+        <v>0.97975403800000005</v>
+      </c>
+      <c r="W3" s="5">
+        <v>0.97701908999999998</v>
+      </c>
+      <c r="X3" s="5">
+        <v>0.97656020600000004</v>
+      </c>
+      <c r="Y3">
+        <v>2937.5</v>
+      </c>
+      <c r="Z3">
+        <v>6.8712809999999999E-3</v>
+      </c>
+      <c r="AA3">
+        <v>3000</v>
+      </c>
+      <c r="AB3">
+        <v>7.0174779999999997E-3</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE3" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK3" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>41</v>
       </c>
-      <c r="O3" t="s">
-        <v>107</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>0</v>
-      </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" t="s">
-        <v>108</v>
-      </c>
-      <c r="U3">
-        <v>21792000</v>
-      </c>
-      <c r="V3" s="5">
-        <v>0.98087371499999998</v>
-      </c>
-      <c r="W3" s="5">
-        <v>0.97975403800000005</v>
-      </c>
-      <c r="X3" s="5">
-        <v>0.97701908999999998</v>
-      </c>
-      <c r="Y3" s="5">
-        <v>0.97656020600000004</v>
-      </c>
-      <c r="Z3">
-        <v>2937.5</v>
-      </c>
-      <c r="AA3">
-        <v>6.8712809999999999E-3</v>
-      </c>
-      <c r="AB3">
-        <v>3000</v>
-      </c>
-      <c r="AC3">
-        <v>7.0174779999999997E-3</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
       <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="C4" s="12">
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>70930767.170000002</v>
       </c>
       <c r="E4">
         <v>70930767.170000002</v>
@@ -2078,129 +1856,126 @@
         <v>70930767.170000002</v>
       </c>
       <c r="G4">
-        <v>70930767.170000002</v>
+        <v>10522.56804</v>
       </c>
       <c r="H4">
-        <v>10522.56804</v>
+        <v>52.518912219999997</v>
       </c>
       <c r="I4">
-        <v>52.518912219999997</v>
+        <v>46.7</v>
       </c>
       <c r="J4">
-        <v>46.7</v>
+        <v>1</v>
       </c>
       <c r="K4">
+        <v>0.37807622099999999</v>
+      </c>
+      <c r="L4">
+        <v>5.7162241000000003E-2</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O4" s="5">
         <v>1</v>
       </c>
-      <c r="L4">
+      <c r="P4" s="5">
         <v>0.37807622099999999</v>
-      </c>
-      <c r="M4">
-        <v>5.7162241000000003E-2</v>
-      </c>
-      <c r="N4" t="s">
-        <v>41</v>
-      </c>
-      <c r="O4" t="s">
-        <v>107</v>
-      </c>
-      <c r="P4" s="5">
-        <v>1</v>
       </c>
       <c r="Q4" s="5">
         <v>0.37807622099999999</v>
       </c>
-      <c r="R4" s="5">
-        <v>0.37807622099999999</v>
+      <c r="R4" t="s">
+        <v>35</v>
       </c>
       <c r="S4" t="s">
+        <v>104</v>
+      </c>
+      <c r="T4">
+        <v>39902000</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0.92891584400000005</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0.91653551200000005</v>
+      </c>
+      <c r="W4" s="5">
+        <v>0.90219036600000002</v>
+      </c>
+      <c r="X4" s="5">
+        <v>0.89919302300000004</v>
+      </c>
+      <c r="Y4">
+        <v>37062.5</v>
+      </c>
+      <c r="Z4">
+        <v>4.9995817999999997E-2</v>
+      </c>
+      <c r="AA4">
+        <v>38085.714290000004</v>
+      </c>
+      <c r="AB4">
+        <v>5.1376092999999998E-2</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T4" t="s">
-        <v>108</v>
-      </c>
-      <c r="U4">
-        <v>39902000</v>
-      </c>
-      <c r="V4" s="5">
-        <v>0.92891584400000005</v>
-      </c>
-      <c r="W4" s="5">
-        <v>0.91653551200000005</v>
-      </c>
-      <c r="X4" s="5">
-        <v>0.90219036600000002</v>
-      </c>
-      <c r="Y4" s="5">
-        <v>0.89919302300000004</v>
-      </c>
-      <c r="Z4">
-        <v>37062.5</v>
-      </c>
-      <c r="AA4">
-        <v>4.9995817999999997E-2</v>
-      </c>
-      <c r="AB4">
-        <v>38085.714290000004</v>
-      </c>
-      <c r="AC4">
-        <v>5.1376092999999998E-2</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="AF4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AK4" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="AL4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AN4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ4" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
+        <v>37</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>30190584.600000001</v>
       </c>
       <c r="E5">
         <v>30190584.600000001</v>
@@ -2209,129 +1984,126 @@
         <v>30190584.600000001</v>
       </c>
       <c r="G5">
-        <v>30190584.600000001</v>
+        <v>58.068975039999998</v>
       </c>
       <c r="H5">
-        <v>58.068975039999998</v>
+        <v>51.512500000000003</v>
       </c>
       <c r="I5">
-        <v>51.512500000000003</v>
+        <v>51.125</v>
       </c>
       <c r="J5">
-        <v>51.125</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" t="s">
+        <v>101</v>
+      </c>
+      <c r="O5" s="5">
         <v>1</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" t="s">
-        <v>105</v>
       </c>
       <c r="P5" s="5">
         <v>1</v>
       </c>
       <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>44</v>
       </c>
       <c r="S5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T5" t="s">
-        <v>106</v>
-      </c>
-      <c r="U5">
+        <v>102</v>
+      </c>
+      <c r="T5">
         <v>24193200</v>
       </c>
+      <c r="U5" s="5">
+        <v>0.89762412599999997</v>
+      </c>
       <c r="V5" s="5">
-        <v>0.89762412599999997</v>
+        <v>0.78116164899999996</v>
       </c>
       <c r="W5" s="5">
-        <v>0.78116164899999996</v>
+        <v>0.76426433900000001</v>
       </c>
       <c r="X5" s="5">
-        <v>0.76426433900000001</v>
-      </c>
-      <c r="Y5" s="5">
         <v>0.75698956699999997</v>
       </c>
+      <c r="Y5">
+        <v>106325</v>
+      </c>
       <c r="Z5">
-        <v>106325</v>
+        <v>0.244803467</v>
       </c>
       <c r="AA5">
-        <v>0.244803467</v>
+        <v>115228.5714</v>
       </c>
       <c r="AB5">
-        <v>115228.5714</v>
-      </c>
-      <c r="AC5">
         <v>0.26530311499999998</v>
       </c>
+      <c r="AC5" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="AD5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AE5" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL5" s="7" t="s">
-        <v>44</v>
+        <v>36</v>
+      </c>
+      <c r="AK5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AN5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AQ5" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>32839120.100000001</v>
       </c>
       <c r="E6">
         <v>32839120.100000001</v>
@@ -2340,129 +2112,126 @@
         <v>32839120.100000001</v>
       </c>
       <c r="G6">
-        <v>32839120.100000001</v>
+        <v>7152.8613930000001</v>
       </c>
       <c r="H6">
-        <v>7152.8613930000001</v>
+        <v>40.719382359999997</v>
       </c>
       <c r="I6">
-        <v>40.719382359999997</v>
+        <v>41.182786649999997</v>
       </c>
       <c r="J6">
-        <v>41.182786649999997</v>
+        <v>1</v>
       </c>
       <c r="K6">
+        <v>0.98654262100000001</v>
+      </c>
+      <c r="L6">
+        <v>0.28333055899999998</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s">
+        <v>101</v>
+      </c>
+      <c r="O6" s="5">
         <v>1</v>
       </c>
-      <c r="L6">
+      <c r="P6" s="5">
         <v>0.98654262100000001</v>
       </c>
-      <c r="M6">
+      <c r="Q6" s="5">
         <v>0.28333055899999998</v>
       </c>
-      <c r="N6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" t="s">
-        <v>105</v>
-      </c>
-      <c r="P6" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>0.98654262100000001</v>
-      </c>
-      <c r="R6" s="5">
-        <v>0.28333055899999998</v>
+      <c r="R6" t="s">
+        <v>35</v>
       </c>
       <c r="S6" t="s">
+        <v>104</v>
+      </c>
+      <c r="T6">
+        <v>29813600</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0.66251643500000001</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0.61594708499999995</v>
+      </c>
+      <c r="W6" s="5">
+        <v>0.57239649000000004</v>
+      </c>
+      <c r="X6" s="5">
+        <v>0.56688222799999999</v>
+      </c>
+      <c r="Y6">
+        <v>89100</v>
+      </c>
+      <c r="Z6">
+        <v>0.22554678</v>
+      </c>
+      <c r="AA6">
+        <v>95957.142860000007</v>
+      </c>
+      <c r="AB6">
+        <v>0.24290487799999999</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE6" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T6" t="s">
-        <v>108</v>
-      </c>
-      <c r="U6">
-        <v>29813600</v>
-      </c>
-      <c r="V6" s="5">
-        <v>0.66251643500000001</v>
-      </c>
-      <c r="W6" s="5">
-        <v>0.61594708499999995</v>
-      </c>
-      <c r="X6" s="5">
-        <v>0.57239649000000004</v>
-      </c>
-      <c r="Y6" s="5">
-        <v>0.56688222799999999</v>
-      </c>
-      <c r="Z6">
-        <v>89100</v>
-      </c>
-      <c r="AA6">
-        <v>0.22554678</v>
-      </c>
-      <c r="AB6">
-        <v>95957.142860000007</v>
-      </c>
-      <c r="AC6">
-        <v>0.24290487799999999</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="AH6" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AK6" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ6" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
+        <v>37</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="C7" s="12">
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>152598212.19999999</v>
       </c>
       <c r="E7">
         <v>152598212.19999999</v>
@@ -2471,129 +2240,126 @@
         <v>152598212.19999999</v>
       </c>
       <c r="G7">
-        <v>152598212.19999999</v>
+        <v>12126.094279999999</v>
       </c>
       <c r="H7">
-        <v>12126.094279999999</v>
+        <v>62.641666669999999</v>
       </c>
       <c r="I7">
-        <v>62.641666669999999</v>
+        <v>59.415833329999998</v>
       </c>
       <c r="J7">
-        <v>59.415833329999998</v>
+        <v>1</v>
       </c>
       <c r="K7">
+        <v>4.8998496000000002E-2</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" t="s">
+        <v>103</v>
+      </c>
+      <c r="O7" s="5">
         <v>1</v>
       </c>
-      <c r="L7">
-        <v>4.8998496000000002E-2</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" t="s">
-        <v>107</v>
-      </c>
       <c r="P7" s="5">
+        <v>0.81791138900000004</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T7">
+        <v>141046800</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0.74287399600000004</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0.69941608</v>
+      </c>
+      <c r="W7" s="5">
+        <v>0.67136865199999995</v>
+      </c>
+      <c r="X7" s="5">
+        <v>0.66667801000000004</v>
+      </c>
+      <c r="Y7">
+        <v>335850</v>
+      </c>
+      <c r="Z7">
+        <v>0.16026436299999999</v>
+      </c>
+      <c r="AA7">
+        <v>360200</v>
+      </c>
+      <c r="AB7">
+        <v>0.17188394700000001</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="12">
         <v>1</v>
       </c>
-      <c r="Q7" s="5">
-        <v>0.81791138900000004</v>
-      </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" t="s">
-        <v>46</v>
-      </c>
-      <c r="T7" t="s">
-        <v>108</v>
-      </c>
-      <c r="U7">
-        <v>141046800</v>
-      </c>
-      <c r="V7" s="5">
-        <v>0.74287399600000004</v>
-      </c>
-      <c r="W7" s="5">
-        <v>0.69941608</v>
-      </c>
-      <c r="X7" s="5">
-        <v>0.67136865199999995</v>
-      </c>
-      <c r="Y7" s="5">
-        <v>0.66667801000000004</v>
-      </c>
-      <c r="Z7">
-        <v>335850</v>
-      </c>
-      <c r="AA7">
-        <v>0.16026436299999999</v>
-      </c>
-      <c r="AB7">
-        <v>360200</v>
-      </c>
-      <c r="AC7">
-        <v>0.17188394700000001</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ7" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
       <c r="D8">
-        <v>1</v>
+        <v>39565.514450000002</v>
       </c>
       <c r="E8">
         <v>39565.514450000002</v>
@@ -2602,16 +2368,16 @@
         <v>39565.514450000002</v>
       </c>
       <c r="G8">
-        <v>39565.514450000002</v>
+        <v>6.0556964999999997E-2</v>
       </c>
       <c r="H8">
-        <v>6.0556964999999997E-2</v>
+        <v>83.924999999999997</v>
       </c>
       <c r="I8">
-        <v>83.924999999999997</v>
+        <v>81.924999999999997</v>
       </c>
       <c r="J8">
-        <v>81.924999999999997</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2619,14 +2385,14 @@
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8">
-        <v>0</v>
+      <c r="M8" t="s">
+        <v>39</v>
       </c>
       <c r="N8" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" t="s">
-        <v>105</v>
+        <v>101</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0</v>
       </c>
       <c r="P8" s="5">
         <v>0</v>
@@ -2634,97 +2400,94 @@
       <c r="Q8" s="5">
         <v>0</v>
       </c>
-      <c r="R8" s="5">
-        <v>0</v>
+      <c r="R8" t="s">
+        <v>35</v>
       </c>
       <c r="S8" t="s">
-        <v>37</v>
-      </c>
-      <c r="T8" t="s">
-        <v>106</v>
-      </c>
-      <c r="U8">
+        <v>102</v>
+      </c>
+      <c r="T8">
         <v>40000</v>
+      </c>
+      <c r="U8" s="5">
+        <v>1</v>
       </c>
       <c r="V8" s="5">
         <v>1</v>
       </c>
       <c r="W8" s="5">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="X8" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="Y8" s="5">
         <v>0.78</v>
       </c>
+      <c r="Y8">
+        <v>275</v>
+      </c>
       <c r="Z8">
-        <v>275</v>
+        <v>0.34375</v>
       </c>
       <c r="AA8">
-        <v>0.34375</v>
+        <v>257.14285710000001</v>
       </c>
       <c r="AB8">
-        <v>257.14285710000001</v>
-      </c>
-      <c r="AC8">
         <v>0.321428571</v>
       </c>
+      <c r="AC8" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="AD8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AE8" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AK8" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AL8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ8" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A9">
+        <v>40</v>
+      </c>
+      <c r="AO8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP8" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
       <c r="D9">
-        <v>8</v>
+        <v>5176403.6749999998</v>
       </c>
       <c r="E9">
         <v>5176403.6749999998</v>
@@ -2733,260 +2496,254 @@
         <v>5176403.6749999998</v>
       </c>
       <c r="G9">
-        <v>5176403.6749999998</v>
+        <v>2474.6930339999999</v>
       </c>
       <c r="H9">
-        <v>2474.6930339999999</v>
+        <v>73.104412460000006</v>
       </c>
       <c r="I9">
-        <v>73.104412460000006</v>
+        <v>72.416912460000006</v>
       </c>
       <c r="J9">
-        <v>72.416912460000006</v>
+        <v>0.58214644100000001</v>
       </c>
       <c r="K9">
         <v>0.58214644100000001</v>
       </c>
       <c r="L9">
+        <v>7.9328339999999997E-3</v>
+      </c>
+      <c r="M9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" t="s">
+        <v>101</v>
+      </c>
+      <c r="O9" s="5">
         <v>0.58214644100000001</v>
-      </c>
-      <c r="M9">
-        <v>7.9328339999999997E-3</v>
-      </c>
-      <c r="N9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9" t="s">
-        <v>105</v>
       </c>
       <c r="P9" s="5">
         <v>0.58214644100000001</v>
       </c>
       <c r="Q9" s="5">
-        <v>0.58214644100000001</v>
-      </c>
-      <c r="R9" s="5">
         <v>7.9328339999999997E-3</v>
       </c>
+      <c r="R9" t="s">
+        <v>35</v>
+      </c>
       <c r="S9" t="s">
+        <v>102</v>
+      </c>
+      <c r="T9">
+        <v>5086000</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0.77451828499999997</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0.76429414100000004</v>
+      </c>
+      <c r="W9" s="5">
+        <v>0.74675579999999997</v>
+      </c>
+      <c r="X9" s="5">
+        <v>0.74290208400000002</v>
+      </c>
+      <c r="Y9">
+        <v>5025</v>
+      </c>
+      <c r="Z9">
+        <v>6.3781985999999999E-2</v>
+      </c>
+      <c r="AA9">
+        <v>5042.8571430000002</v>
+      </c>
+      <c r="AB9">
+        <v>6.4008646000000002E-2</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T9" t="s">
-        <v>106</v>
-      </c>
-      <c r="U9">
-        <v>5086000</v>
-      </c>
-      <c r="V9" s="5">
-        <v>0.77451828499999997</v>
-      </c>
-      <c r="W9" s="5">
-        <v>0.76429414100000004</v>
-      </c>
-      <c r="X9" s="5">
-        <v>0.74675579999999997</v>
-      </c>
-      <c r="Y9" s="5">
-        <v>0.74290208400000002</v>
-      </c>
-      <c r="Z9">
-        <v>5025</v>
-      </c>
-      <c r="AA9">
-        <v>6.3781985999999999E-2</v>
-      </c>
-      <c r="AB9">
-        <v>5042.8571430000002</v>
-      </c>
-      <c r="AC9">
-        <v>6.4008646000000002E-2</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AM9" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="AN9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:42" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="15">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>30105647.129999999</v>
+      </c>
+      <c r="E10" s="6">
+        <v>30105647.129999999</v>
+      </c>
+      <c r="F10" s="6">
+        <v>30105647.129999999</v>
+      </c>
+      <c r="G10" s="6">
+        <v>51.287457760000002</v>
+      </c>
+      <c r="H10" s="6">
+        <v>78</v>
+      </c>
+      <c r="I10" s="6">
+        <v>78</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AO9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:43" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="s">
+      <c r="N10" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="T10" s="6">
+        <v>20660800</v>
+      </c>
+      <c r="U10" s="9">
+        <v>0.64915201700000003</v>
+      </c>
+      <c r="V10" s="9">
+        <v>0.61025710499999997</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0.58233950300000004</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0.58086811699999996</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>44087.5</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>0.16435841000000001</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>49300</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>0.18379063500000001</v>
+      </c>
+      <c r="AC10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK10" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO10" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP10" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="11">
-        <v>1</v>
-      </c>
-      <c r="E10" s="11">
-        <v>30105647.129999999</v>
-      </c>
-      <c r="F10" s="11">
-        <v>30105647.129999999</v>
-      </c>
-      <c r="G10" s="11">
-        <v>30105647.129999999</v>
-      </c>
-      <c r="H10" s="11">
-        <v>51.287457760000002</v>
-      </c>
-      <c r="I10" s="11">
-        <v>78</v>
-      </c>
-      <c r="J10" s="11">
-        <v>78</v>
-      </c>
-      <c r="K10" s="11">
-        <v>0</v>
-      </c>
-      <c r="L10" s="11">
-        <v>0</v>
-      </c>
-      <c r="M10" s="11">
-        <v>0</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="P10" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>0</v>
-      </c>
-      <c r="R10" s="12">
-        <v>0</v>
-      </c>
-      <c r="S10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T10" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="U10" s="11">
-        <v>20660800</v>
-      </c>
-      <c r="V10" s="12">
-        <v>0.64915201700000003</v>
-      </c>
-      <c r="W10" s="12">
-        <v>0.61025710499999997</v>
-      </c>
-      <c r="X10" s="12">
-        <v>0.58233950300000004</v>
-      </c>
-      <c r="Y10" s="12">
-        <v>0.58086811699999996</v>
-      </c>
-      <c r="Z10" s="11">
-        <v>44087.5</v>
-      </c>
-      <c r="AA10" s="11">
-        <v>0.16435841000000001</v>
-      </c>
-      <c r="AB10" s="11">
-        <v>49300</v>
-      </c>
-      <c r="AC10" s="11">
-        <v>0.18379063500000001</v>
-      </c>
-      <c r="AD10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP10" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ10" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:43" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
       <c r="B11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="C11" s="15">
+        <v>3</v>
       </c>
       <c r="D11" s="6">
-        <v>3</v>
+        <v>143423569.5</v>
       </c>
       <c r="E11" s="6">
         <v>143423569.5</v>
@@ -2995,129 +2752,126 @@
         <v>143423569.5</v>
       </c>
       <c r="G11" s="6">
-        <v>143423569.5</v>
+        <v>3228.0579069999999</v>
       </c>
       <c r="H11" s="6">
-        <v>3228.0579069999999</v>
+        <v>70.216255849999996</v>
       </c>
       <c r="I11" s="6">
         <v>70.216255849999996</v>
       </c>
       <c r="J11" s="6">
-        <v>70.216255849999996</v>
+        <v>0.84882266200000001</v>
       </c>
       <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="O11" s="9">
         <v>0.84882266200000001</v>
       </c>
-      <c r="L11" s="6">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="6" t="s">
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="T11" s="6">
+        <v>127636000</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0.58799398300000005</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0.56836942599999996</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0.542781034</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0.54014227999999997</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>190862.5</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0.127158251</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>206100</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>0.137309925</v>
+      </c>
+      <c r="AC11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE11" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK11" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO11" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="P11" s="10">
-        <v>0.84882266200000001</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>0</v>
-      </c>
-      <c r="R11" s="10">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6" t="s">
+      <c r="AP11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="T11" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="U11" s="6">
-        <v>127636000</v>
-      </c>
-      <c r="V11" s="10">
-        <v>0.58799398300000005</v>
-      </c>
-      <c r="W11" s="10">
-        <v>0.56836942599999996</v>
-      </c>
-      <c r="X11" s="10">
-        <v>0.542781034</v>
-      </c>
-      <c r="Y11" s="10">
-        <v>0.54014227999999997</v>
-      </c>
-      <c r="Z11" s="6">
-        <v>190862.5</v>
-      </c>
-      <c r="AA11" s="6">
-        <v>0.127158251</v>
-      </c>
-      <c r="AB11" s="6">
-        <v>206100</v>
-      </c>
-      <c r="AC11" s="6">
-        <v>0.137309925</v>
-      </c>
-      <c r="AD11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AM11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="AQ11" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
+    </row>
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>5725821.1289999997</v>
       </c>
       <c r="E12">
         <v>5725821.1289999997</v>
@@ -3126,129 +2880,126 @@
         <v>5725821.1289999997</v>
       </c>
       <c r="G12">
-        <v>5725821.1289999997</v>
+        <v>32.858326939999998</v>
       </c>
       <c r="H12">
-        <v>32.858326939999998</v>
+        <v>72.861300659999998</v>
       </c>
       <c r="I12">
-        <v>72.861300659999998</v>
+        <v>68.208333330000002</v>
       </c>
       <c r="J12">
-        <v>68.208333330000002</v>
+        <v>1</v>
       </c>
       <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" t="s">
+        <v>103</v>
+      </c>
+      <c r="O12" s="5">
         <v>1</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" t="s">
-        <v>107</v>
-      </c>
       <c r="P12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="5">
         <v>0</v>
       </c>
-      <c r="R12" s="5">
-        <v>0</v>
+      <c r="R12" t="s">
+        <v>35</v>
       </c>
       <c r="S12" t="s">
-        <v>37</v>
-      </c>
-      <c r="T12" t="s">
-        <v>108</v>
-      </c>
-      <c r="U12">
+        <v>104</v>
+      </c>
+      <c r="T12">
         <v>5728800</v>
       </c>
+      <c r="U12" s="5">
+        <v>0.99245915399999995</v>
+      </c>
       <c r="V12" s="5">
-        <v>0.99245915399999995</v>
+        <v>0.99231950800000002</v>
       </c>
       <c r="W12" s="5">
-        <v>0.99231950800000002</v>
+        <v>0.98882837599999995</v>
       </c>
       <c r="X12" s="5">
-        <v>0.98882837599999995</v>
-      </c>
-      <c r="Y12" s="5">
         <v>0.98861890799999996</v>
       </c>
+      <c r="Y12">
+        <v>687.5</v>
+      </c>
       <c r="Z12">
-        <v>687.5</v>
+        <v>6.0459759999999998E-3</v>
       </c>
       <c r="AA12">
-        <v>6.0459759999999998E-3</v>
+        <v>742.85714289999999</v>
       </c>
       <c r="AB12">
-        <v>742.85714289999999</v>
-      </c>
-      <c r="AC12">
         <v>6.5327950000000001E-3</v>
       </c>
+      <c r="AC12" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="AD12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AE12" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AH12" s="1" t="s">
         <v>42</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL12" s="7" t="s">
-        <v>44</v>
+        <v>36</v>
+      </c>
+      <c r="AK12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL12" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AO12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ12" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
+        <v>40</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP12" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="C13">
+        <v>40</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>69259667.319999993</v>
       </c>
       <c r="E13">
         <v>69259667.319999993</v>
@@ -3257,129 +3008,126 @@
         <v>69259667.319999993</v>
       </c>
       <c r="G13">
-        <v>69259667.319999993</v>
+        <v>37350.573799999998</v>
       </c>
       <c r="H13">
-        <v>37350.573799999998</v>
+        <v>79.160080030000003</v>
       </c>
       <c r="I13">
-        <v>79.160080030000003</v>
+        <v>78.332189209999996</v>
       </c>
       <c r="J13">
-        <v>78.332189209999996</v>
+        <v>0.40921797300000001</v>
       </c>
       <c r="K13">
-        <v>0.40921797300000001</v>
+        <v>0.213309887</v>
       </c>
       <c r="L13">
+        <v>6.4030007E-2</v>
+      </c>
+      <c r="M13" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" t="s">
+        <v>101</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0.37957716699999999</v>
+      </c>
+      <c r="P13" s="5">
         <v>0.213309887</v>
       </c>
-      <c r="M13">
+      <c r="Q13" s="5">
         <v>6.4030007E-2</v>
       </c>
-      <c r="N13" t="s">
-        <v>36</v>
-      </c>
-      <c r="O13" t="s">
-        <v>105</v>
-      </c>
-      <c r="P13" s="5">
-        <v>0.37957716699999999</v>
-      </c>
-      <c r="Q13" s="5">
-        <v>0.213309887</v>
-      </c>
-      <c r="R13" s="5">
-        <v>6.4030007E-2</v>
+      <c r="R13" t="s">
+        <v>35</v>
       </c>
       <c r="S13" t="s">
-        <v>37</v>
-      </c>
-      <c r="T13" t="s">
-        <v>108</v>
-      </c>
-      <c r="U13">
+        <v>104</v>
+      </c>
+      <c r="T13">
         <v>65765600</v>
       </c>
+      <c r="U13" s="5">
+        <v>0.81061223500000001</v>
+      </c>
       <c r="V13" s="5">
-        <v>0.81061223500000001</v>
+        <v>0.792061503</v>
       </c>
       <c r="W13" s="5">
-        <v>0.792061503</v>
+        <v>0.76678385100000002</v>
       </c>
       <c r="X13" s="5">
-        <v>0.76678385100000002</v>
-      </c>
-      <c r="Y13" s="5">
         <v>0.76395562400000006</v>
       </c>
+      <c r="Y13">
+        <v>95887.5</v>
+      </c>
       <c r="Z13">
-        <v>95887.5</v>
+        <v>8.9933203000000003E-2</v>
       </c>
       <c r="AA13">
-        <v>8.9933203000000003E-2</v>
+        <v>102942.85709999999</v>
       </c>
       <c r="AB13">
-        <v>102942.85709999999</v>
-      </c>
-      <c r="AC13">
         <v>9.6550444999999999E-2</v>
       </c>
+      <c r="AC13" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="AD13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AE13" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL13" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="AK13" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL13" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ13" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="AO13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP13" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>176692482.90000001</v>
       </c>
       <c r="E14">
         <v>176692482.90000001</v>
@@ -3388,129 +3136,126 @@
         <v>176692482.90000001</v>
       </c>
       <c r="G14">
-        <v>176692482.90000001</v>
+        <v>52659.212639999998</v>
       </c>
       <c r="H14">
-        <v>52659.212639999998</v>
+        <v>75.861034529999998</v>
       </c>
       <c r="I14">
-        <v>75.861034529999998</v>
+        <v>72.618647170000003</v>
       </c>
       <c r="J14">
-        <v>72.618647170000003</v>
+        <v>0.46975134499999999</v>
       </c>
       <c r="K14">
-        <v>0.46975134499999999</v>
+        <v>0.21245858500000001</v>
       </c>
       <c r="L14">
-        <v>0.21245858500000001</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>34</v>
       </c>
       <c r="N14" t="s">
-        <v>36</v>
-      </c>
-      <c r="O14" t="s">
-        <v>107</v>
+        <v>103</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0.72013926399999995</v>
       </c>
       <c r="P14" s="5">
-        <v>0.72013926399999995</v>
+        <v>0.29044295399999998</v>
       </c>
       <c r="Q14" s="5">
-        <v>0.29044295399999998</v>
-      </c>
-      <c r="R14" s="5">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>44</v>
       </c>
       <c r="S14" t="s">
-        <v>46</v>
-      </c>
-      <c r="T14" t="s">
-        <v>108</v>
-      </c>
-      <c r="U14">
+        <v>104</v>
+      </c>
+      <c r="T14">
         <v>146254400</v>
       </c>
+      <c r="U14" s="5">
+        <v>0.74294380199999999</v>
+      </c>
       <c r="V14" s="5">
-        <v>0.74294380199999999</v>
+        <v>0.70852159000000003</v>
       </c>
       <c r="W14" s="5">
-        <v>0.70852159000000003</v>
+        <v>0.681248564</v>
       </c>
       <c r="X14" s="5">
-        <v>0.681248564</v>
-      </c>
-      <c r="Y14" s="5">
         <v>0.67681245800000001</v>
       </c>
+      <c r="Y14">
+        <v>302250</v>
+      </c>
       <c r="Z14">
-        <v>302250</v>
+        <v>0.13908215400000001</v>
       </c>
       <c r="AA14">
-        <v>0.13908215400000001</v>
+        <v>322257.14289999998</v>
       </c>
       <c r="AB14">
-        <v>322257.14289999998</v>
-      </c>
-      <c r="AC14">
         <v>0.14828856100000001</v>
       </c>
+      <c r="AC14" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="AD14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AE14" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AK14" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ14" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
+        <v>36</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>1224358.2990000001</v>
       </c>
       <c r="E15">
         <v>1224358.2990000001</v>
@@ -3519,16 +3264,16 @@
         <v>1224358.2990000001</v>
       </c>
       <c r="G15">
-        <v>1224358.2990000001</v>
+        <v>105.9750087</v>
       </c>
       <c r="H15">
-        <v>105.9750087</v>
+        <v>93.621623170000007</v>
       </c>
       <c r="I15">
-        <v>93.621623170000007</v>
+        <v>91.663289840000004</v>
       </c>
       <c r="J15">
-        <v>91.663289840000004</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -3536,14 +3281,14 @@
       <c r="L15">
         <v>0</v>
       </c>
-      <c r="M15">
-        <v>0</v>
+      <c r="M15" t="s">
+        <v>39</v>
       </c>
       <c r="N15" t="s">
-        <v>41</v>
-      </c>
-      <c r="O15" t="s">
-        <v>105</v>
+        <v>101</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0</v>
       </c>
       <c r="P15" s="5">
         <v>0</v>
@@ -3551,97 +3296,94 @@
       <c r="Q15" s="5">
         <v>0</v>
       </c>
-      <c r="R15" s="5">
-        <v>0</v>
+      <c r="R15" t="s">
+        <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>37</v>
-      </c>
-      <c r="T15" t="s">
-        <v>106</v>
-      </c>
-      <c r="U15">
+        <v>102</v>
+      </c>
+      <c r="T15">
         <v>1212800</v>
+      </c>
+      <c r="U15" s="5">
+        <v>1</v>
       </c>
       <c r="V15" s="5">
         <v>1</v>
       </c>
       <c r="W15" s="5">
-        <v>1</v>
+        <v>0.95580474900000001</v>
       </c>
       <c r="X15" s="5">
-        <v>0.95580474900000001</v>
-      </c>
-      <c r="Y15" s="5">
         <v>0.94986807399999995</v>
       </c>
+      <c r="Y15">
+        <v>1900</v>
+      </c>
       <c r="Z15">
-        <v>1900</v>
+        <v>7.8331134999999996E-2</v>
       </c>
       <c r="AA15">
-        <v>7.8331134999999996E-2</v>
+        <v>1914.2857140000001</v>
       </c>
       <c r="AB15">
-        <v>1914.2857140000001</v>
-      </c>
-      <c r="AC15">
         <v>7.8920089999999998E-2</v>
       </c>
+      <c r="AC15" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="AD15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AE15" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AK15" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ15" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP15" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>48</v>
       </c>
       <c r="D16">
-        <v>48</v>
+        <v>16102721.17</v>
       </c>
       <c r="E16">
         <v>16102721.17</v>
@@ -3650,129 +3392,126 @@
         <v>16102721.17</v>
       </c>
       <c r="G16">
-        <v>16102721.17</v>
+        <v>40842.686459999997</v>
       </c>
       <c r="H16">
-        <v>40842.686459999997</v>
+        <v>79.012235680000003</v>
       </c>
       <c r="I16">
-        <v>79.012235680000003</v>
+        <v>76.70347323</v>
       </c>
       <c r="J16">
-        <v>76.70347323</v>
+        <v>0.19930187399999999</v>
       </c>
       <c r="K16">
-        <v>0.19930187399999999</v>
+        <v>8.7016045E-2</v>
       </c>
       <c r="L16">
-        <v>8.7016045E-2</v>
-      </c>
-      <c r="M16">
         <v>7.8133440999999998E-2</v>
       </c>
+      <c r="M16" t="s">
+        <v>39</v>
+      </c>
       <c r="N16" t="s">
-        <v>41</v>
-      </c>
-      <c r="O16" t="s">
-        <v>105</v>
+        <v>101</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0.27661379600000002</v>
       </c>
       <c r="P16" s="5">
-        <v>0.27661379600000002</v>
+        <v>9.1899365999999996E-2</v>
       </c>
       <c r="Q16" s="5">
-        <v>9.1899365999999996E-2</v>
-      </c>
-      <c r="R16" s="5">
         <v>7.8133440999999998E-2</v>
       </c>
+      <c r="R16" t="s">
+        <v>35</v>
+      </c>
       <c r="S16" t="s">
-        <v>37</v>
-      </c>
-      <c r="T16" t="s">
-        <v>106</v>
-      </c>
-      <c r="U16">
+        <v>102</v>
+      </c>
+      <c r="T16">
         <v>15638000</v>
       </c>
+      <c r="U16" s="5">
+        <v>0.93815065900000005</v>
+      </c>
       <c r="V16" s="5">
-        <v>0.93815065900000005</v>
+        <v>0.92546361399999999</v>
       </c>
       <c r="W16" s="5">
-        <v>0.92546361399999999</v>
+        <v>0.91349277399999995</v>
       </c>
       <c r="X16" s="5">
-        <v>0.91349277399999995</v>
-      </c>
-      <c r="Y16" s="5">
         <v>0.91101163799999996</v>
       </c>
+      <c r="Y16">
+        <v>13262.5</v>
+      </c>
       <c r="Z16">
-        <v>13262.5</v>
+        <v>4.5200329999999997E-2</v>
       </c>
       <c r="AA16">
-        <v>4.5200329999999997E-2</v>
+        <v>13771.42857</v>
       </c>
       <c r="AB16">
-        <v>13771.42857</v>
-      </c>
-      <c r="AC16">
         <v>4.6934824999999999E-2</v>
       </c>
+      <c r="AC16" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="AD16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AE16" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AK16" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AQ16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
+        <v>36</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C17" s="12">
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>28152019.879999999</v>
       </c>
       <c r="E17">
         <v>28152019.879999999</v>
@@ -3781,16 +3520,16 @@
         <v>28152019.879999999</v>
       </c>
       <c r="G17">
-        <v>28152019.879999999</v>
+        <v>43.816871470000002</v>
       </c>
       <c r="H17">
-        <v>43.816871470000002</v>
+        <v>26.26047294</v>
       </c>
       <c r="I17">
         <v>26.26047294</v>
       </c>
       <c r="J17">
-        <v>26.26047294</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -3798,14 +3537,14 @@
       <c r="L17">
         <v>1</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="s">
+        <v>34</v>
+      </c>
+      <c r="N17" t="s">
+        <v>103</v>
+      </c>
+      <c r="O17" s="5">
         <v>1</v>
-      </c>
-      <c r="N17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O17" t="s">
-        <v>107</v>
       </c>
       <c r="P17" s="5">
         <v>1</v>
@@ -3813,97 +3552,94 @@
       <c r="Q17" s="5">
         <v>1</v>
       </c>
-      <c r="R17" s="5">
-        <v>1</v>
+      <c r="R17" t="s">
+        <v>44</v>
       </c>
       <c r="S17" t="s">
-        <v>46</v>
-      </c>
-      <c r="T17" t="s">
-        <v>108</v>
-      </c>
-      <c r="U17">
+        <v>104</v>
+      </c>
+      <c r="T17">
         <v>28152800</v>
       </c>
+      <c r="U17" s="5">
+        <v>0.45582677399999999</v>
+      </c>
       <c r="V17" s="5">
-        <v>0.45582677399999999</v>
+        <v>0.41531925800000002</v>
       </c>
       <c r="W17" s="5">
-        <v>0.41531925800000002</v>
+        <v>0.328294166</v>
       </c>
       <c r="X17" s="5">
-        <v>0.328294166</v>
-      </c>
-      <c r="Y17" s="5">
         <v>0.31988292499999998</v>
       </c>
+      <c r="Y17">
+        <v>119600</v>
+      </c>
       <c r="Z17">
-        <v>119600</v>
+        <v>0.46599339200000001</v>
       </c>
       <c r="AA17">
-        <v>0.46599339200000001</v>
+        <v>128228.5714</v>
       </c>
       <c r="AB17">
-        <v>128228.5714</v>
-      </c>
-      <c r="AC17">
         <v>0.49961260000000002</v>
       </c>
+      <c r="AC17" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="AD17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE17" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AE17" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AF17" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AG17" s="1" t="s">
         <v>42</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK17" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AK17" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AL17" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM17" s="1" t="s">
         <v>42</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AQ17" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AP17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C18" s="12">
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>818752767.5</v>
       </c>
       <c r="E18">
         <v>818752767.5</v>
@@ -3912,129 +3648,126 @@
         <v>818752767.5</v>
       </c>
       <c r="G18">
-        <v>818752767.5</v>
+        <v>3408.7885040000001</v>
       </c>
       <c r="H18">
-        <v>3408.7885040000001</v>
+        <v>42.887500000000003</v>
       </c>
       <c r="I18">
-        <v>42.887500000000003</v>
+        <v>39.8125</v>
       </c>
       <c r="J18">
-        <v>39.8125</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18">
+        <v>2.2909504000000001E-2</v>
+      </c>
+      <c r="M18" t="s">
+        <v>34</v>
+      </c>
+      <c r="N18" t="s">
+        <v>103</v>
+      </c>
+      <c r="O18" s="5">
         <v>1</v>
-      </c>
-      <c r="M18">
-        <v>2.2909504000000001E-2</v>
-      </c>
-      <c r="N18" t="s">
-        <v>36</v>
-      </c>
-      <c r="O18" t="s">
-        <v>107</v>
       </c>
       <c r="P18" s="5">
         <v>1</v>
       </c>
       <c r="Q18" s="5">
-        <v>1</v>
-      </c>
-      <c r="R18" s="5">
         <v>0.100650588</v>
       </c>
+      <c r="R18" t="s">
+        <v>44</v>
+      </c>
       <c r="S18" t="s">
-        <v>46</v>
-      </c>
-      <c r="T18" t="s">
-        <v>108</v>
-      </c>
-      <c r="U18">
+        <v>104</v>
+      </c>
+      <c r="T18">
         <v>507128400</v>
       </c>
+      <c r="U18" s="5">
+        <v>0.82955638099999995</v>
+      </c>
       <c r="V18" s="5">
-        <v>0.82955638099999995</v>
+        <v>0.80344938300000002</v>
       </c>
       <c r="W18" s="5">
-        <v>0.80344938300000002</v>
+        <v>0.79155338200000003</v>
       </c>
       <c r="X18" s="5">
-        <v>0.79155338200000003</v>
-      </c>
-      <c r="Y18" s="5">
         <v>0.76552920300000005</v>
       </c>
+      <c r="Y18">
+        <v>1014687.5</v>
+      </c>
       <c r="Z18">
-        <v>1014687.5</v>
+        <v>0.120597547</v>
       </c>
       <c r="AA18">
-        <v>0.120597547</v>
+        <v>688300</v>
       </c>
       <c r="AB18">
-        <v>688300</v>
-      </c>
-      <c r="AC18">
         <v>8.1805769E-2</v>
       </c>
+      <c r="AC18" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="AD18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE18" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AE18" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AH18" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AI18" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AJ18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK18" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AK18" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="AL18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AN18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ18" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
+        <v>37</v>
+      </c>
+      <c r="AO18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP18" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>107658288.5</v>
       </c>
       <c r="E19">
         <v>107658288.5</v>
@@ -4043,129 +3776,126 @@
         <v>107658288.5</v>
       </c>
       <c r="G19">
-        <v>107658288.5</v>
+        <v>12918.34117</v>
       </c>
       <c r="H19">
-        <v>12918.34117</v>
+        <v>66.228999999999999</v>
       </c>
       <c r="I19">
-        <v>66.228999999999999</v>
+        <v>63.583166669999997</v>
       </c>
       <c r="J19">
-        <v>63.583166669999997</v>
+        <v>0.87809277200000002</v>
       </c>
       <c r="K19">
         <v>0.87809277200000002</v>
       </c>
       <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>34</v>
+      </c>
+      <c r="N19" t="s">
+        <v>103</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0.92172678200000002</v>
+      </c>
+      <c r="P19" s="5">
         <v>0.87809277200000002</v>
       </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>36</v>
-      </c>
-      <c r="O19" t="s">
-        <v>107</v>
-      </c>
-      <c r="P19" s="5">
-        <v>0.92172678200000002</v>
-      </c>
       <c r="Q19" s="5">
-        <v>0.87809277200000002</v>
-      </c>
-      <c r="R19" s="5">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>35</v>
       </c>
       <c r="S19" t="s">
+        <v>104</v>
+      </c>
+      <c r="T19">
+        <v>104650000</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0.667042523</v>
+      </c>
+      <c r="V19" s="5">
+        <v>0.53476923099999996</v>
+      </c>
+      <c r="W19" s="5">
+        <v>0.52310750100000003</v>
+      </c>
+      <c r="X19" s="5">
+        <v>0.52104347799999995</v>
+      </c>
+      <c r="Y19">
+        <v>477462.5</v>
+      </c>
+      <c r="Z19">
+        <v>0.34199245099999998</v>
+      </c>
+      <c r="AA19">
+        <v>537957.14289999998</v>
+      </c>
+      <c r="AB19">
+        <v>0.385322997</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE19" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T19" t="s">
-        <v>108</v>
-      </c>
-      <c r="U19">
-        <v>104650000</v>
-      </c>
-      <c r="V19" s="5">
-        <v>0.667042523</v>
-      </c>
-      <c r="W19" s="5">
-        <v>0.53476923099999996</v>
-      </c>
-      <c r="X19" s="5">
-        <v>0.52310750100000003</v>
-      </c>
-      <c r="Y19" s="5">
-        <v>0.52104347799999995</v>
-      </c>
-      <c r="Z19">
-        <v>477462.5</v>
-      </c>
-      <c r="AA19">
-        <v>0.34199245099999998</v>
-      </c>
-      <c r="AB19">
-        <v>537957.14289999998</v>
-      </c>
-      <c r="AC19">
-        <v>0.385322997</v>
-      </c>
-      <c r="AD19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE19" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="AF19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="AK19" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="AL19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AN19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ19" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C20">
+        <v>44</v>
       </c>
       <c r="D20">
-        <v>44</v>
+        <v>50512089.759999998</v>
       </c>
       <c r="E20">
         <v>50512089.759999998</v>
@@ -4174,129 +3904,126 @@
         <v>50512089.759999998</v>
       </c>
       <c r="G20">
-        <v>50512089.759999998</v>
+        <v>6359.6927649999998</v>
       </c>
       <c r="H20">
-        <v>6359.6927649999998</v>
+        <v>71.024149170000001</v>
       </c>
       <c r="I20">
-        <v>71.024149170000001</v>
+        <v>69.972899170000005</v>
       </c>
       <c r="J20">
-        <v>69.972899170000005</v>
+        <v>0.56399410100000003</v>
       </c>
       <c r="K20">
-        <v>0.56399410100000003</v>
+        <v>0.168977134</v>
       </c>
       <c r="L20">
+        <v>1.7691618999999999E-2</v>
+      </c>
+      <c r="M20" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" t="s">
+        <v>103</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0.57512781099999999</v>
+      </c>
+      <c r="P20" s="5">
         <v>0.168977134</v>
       </c>
-      <c r="M20">
-        <v>1.7691618999999999E-2</v>
-      </c>
-      <c r="N20" t="s">
-        <v>41</v>
-      </c>
-      <c r="O20" t="s">
-        <v>107</v>
-      </c>
-      <c r="P20" s="5">
-        <v>0.57512781099999999</v>
-      </c>
       <c r="Q20" s="5">
-        <v>0.168977134</v>
-      </c>
-      <c r="R20" s="5">
         <v>2.7649720999999999E-2</v>
       </c>
+      <c r="R20" t="s">
+        <v>35</v>
+      </c>
       <c r="S20" t="s">
+        <v>104</v>
+      </c>
+      <c r="T20">
+        <v>49578400</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0.66545915200000005</v>
+      </c>
+      <c r="V20" s="5">
+        <v>0.61148403299999998</v>
+      </c>
+      <c r="W20" s="5">
+        <v>0.58827231199999996</v>
+      </c>
+      <c r="X20" s="5">
+        <v>0.58553725000000001</v>
+      </c>
+      <c r="Y20">
+        <v>123825</v>
+      </c>
+      <c r="Z20">
+        <v>0.18765685400000001</v>
+      </c>
+      <c r="AA20">
+        <v>136671.42860000001</v>
+      </c>
+      <c r="AB20">
+        <v>0.20712562400000001</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE20" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T20" t="s">
-        <v>108</v>
-      </c>
-      <c r="U20">
-        <v>49578400</v>
-      </c>
-      <c r="V20" s="5">
-        <v>0.66545915200000005</v>
-      </c>
-      <c r="W20" s="5">
-        <v>0.61148403299999998</v>
-      </c>
-      <c r="X20" s="5">
-        <v>0.58827231199999996</v>
-      </c>
-      <c r="Y20" s="5">
-        <v>0.58553725000000001</v>
-      </c>
-      <c r="Z20">
-        <v>123825</v>
-      </c>
-      <c r="AA20">
-        <v>0.18765685400000001</v>
-      </c>
-      <c r="AB20">
-        <v>136671.42860000001</v>
-      </c>
-      <c r="AC20">
-        <v>0.20712562400000001</v>
-      </c>
-      <c r="AD20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE20" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="AF20" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI20" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL20" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="AK20" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AM20" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AQ20" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="AO20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C21">
+        <v>17</v>
       </c>
       <c r="D21">
-        <v>17</v>
+        <v>78499142.019999996</v>
       </c>
       <c r="E21">
         <v>78499142.019999996</v>
@@ -4305,129 +4032,126 @@
         <v>78499142.019999996</v>
       </c>
       <c r="G21">
-        <v>78499142.019999996</v>
+        <v>8874.8979729999992</v>
       </c>
       <c r="H21">
-        <v>8874.8979729999992</v>
+        <v>76.337534829999996</v>
       </c>
       <c r="I21">
-        <v>76.337534829999996</v>
+        <v>74.274107360000002</v>
       </c>
       <c r="J21">
-        <v>74.274107360000002</v>
+        <v>0.252929776</v>
       </c>
       <c r="K21">
-        <v>0.252929776</v>
+        <v>0.14114576300000001</v>
       </c>
       <c r="L21">
         <v>0.14114576300000001</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="s">
+        <v>39</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0.40364180399999999</v>
+      </c>
+      <c r="P21" s="5">
         <v>0.14114576300000001</v>
-      </c>
-      <c r="N21" t="s">
-        <v>41</v>
-      </c>
-      <c r="O21" t="s">
-        <v>107</v>
-      </c>
-      <c r="P21" s="5">
-        <v>0.40364180399999999</v>
       </c>
       <c r="Q21" s="5">
         <v>0.14114576300000001</v>
       </c>
-      <c r="R21" s="5">
-        <v>0.14114576300000001</v>
+      <c r="R21" t="s">
+        <v>35</v>
       </c>
       <c r="S21" t="s">
+        <v>104</v>
+      </c>
+      <c r="T21">
+        <v>70417200</v>
+      </c>
+      <c r="U21" s="5">
+        <v>0.59101469500000003</v>
+      </c>
+      <c r="V21" s="5">
+        <v>0.54446356900000004</v>
+      </c>
+      <c r="W21" s="5">
+        <v>0.52236669499999999</v>
+      </c>
+      <c r="X21" s="5">
+        <v>0.51852672399999999</v>
+      </c>
+      <c r="Y21">
+        <v>159512.5</v>
+      </c>
+      <c r="Z21">
+        <v>0.19164067600000001</v>
+      </c>
+      <c r="AA21">
+        <v>172642.85709999999</v>
+      </c>
+      <c r="AB21">
+        <v>0.20741568099999999</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE21" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T21" t="s">
-        <v>108</v>
-      </c>
-      <c r="U21">
-        <v>70417200</v>
-      </c>
-      <c r="V21" s="5">
-        <v>0.59101469500000003</v>
-      </c>
-      <c r="W21" s="5">
-        <v>0.54446356900000004</v>
-      </c>
-      <c r="X21" s="5">
-        <v>0.52236669499999999</v>
-      </c>
-      <c r="Y21" s="5">
-        <v>0.51852672399999999</v>
-      </c>
-      <c r="Z21">
-        <v>159512.5</v>
-      </c>
-      <c r="AA21">
-        <v>0.19164067600000001</v>
-      </c>
-      <c r="AB21">
-        <v>172642.85709999999</v>
-      </c>
-      <c r="AC21">
-        <v>0.20741568099999999</v>
-      </c>
-      <c r="AD21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE21" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="AF21" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI21" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL21" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="AK21" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL21" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP21" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AQ21" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
+        <v>36</v>
+      </c>
+      <c r="AO21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP21" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22">
         <v>60</v>
       </c>
       <c r="D22">
-        <v>60</v>
+        <v>20483903.66</v>
       </c>
       <c r="E22">
         <v>20483903.66</v>
@@ -4436,129 +4160,126 @@
         <v>20483903.66</v>
       </c>
       <c r="G22">
-        <v>20483903.66</v>
+        <v>6668.4366710000004</v>
       </c>
       <c r="H22">
-        <v>6668.4366710000004</v>
+        <v>77.944216490000002</v>
       </c>
       <c r="I22">
-        <v>77.944216490000002</v>
+        <v>77.188042519999996</v>
       </c>
       <c r="J22">
-        <v>77.188042519999996</v>
+        <v>0.38530308899999999</v>
       </c>
       <c r="K22">
+        <v>0.12498224500000001</v>
+      </c>
+      <c r="L22">
+        <v>8.8053930000000002E-2</v>
+      </c>
+      <c r="M22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" t="s">
+        <v>101</v>
+      </c>
+      <c r="O22" s="5">
         <v>0.38530308899999999</v>
       </c>
-      <c r="L22">
+      <c r="P22" s="5">
         <v>0.12498224500000001</v>
       </c>
-      <c r="M22">
-        <v>8.8053930000000002E-2</v>
-      </c>
-      <c r="N22" t="s">
-        <v>36</v>
-      </c>
-      <c r="O22" t="s">
-        <v>105</v>
-      </c>
-      <c r="P22" s="5">
-        <v>0.38530308899999999</v>
-      </c>
       <c r="Q22" s="5">
-        <v>0.12498224500000001</v>
-      </c>
-      <c r="R22" s="5">
         <v>0.109919537</v>
       </c>
+      <c r="R22" t="s">
+        <v>35</v>
+      </c>
       <c r="S22" t="s">
+        <v>104</v>
+      </c>
+      <c r="T22">
+        <v>20405200</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0.80114872699999995</v>
+      </c>
+      <c r="V22" s="5">
+        <v>0.78991629600000002</v>
+      </c>
+      <c r="W22" s="5">
+        <v>0.77290102500000002</v>
+      </c>
+      <c r="X22" s="5">
+        <v>0.77113676900000006</v>
+      </c>
+      <c r="Y22">
+        <v>19137.5</v>
+      </c>
+      <c r="Z22">
+        <v>5.8533056999999999E-2</v>
+      </c>
+      <c r="AA22">
+        <v>20585.71429</v>
+      </c>
+      <c r="AB22">
+        <v>6.2962497000000006E-2</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE22" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK22" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T22" t="s">
-        <v>108</v>
-      </c>
-      <c r="U22">
-        <v>20405200</v>
-      </c>
-      <c r="V22" s="5">
-        <v>0.80114872699999995</v>
-      </c>
-      <c r="W22" s="5">
-        <v>0.78991629600000002</v>
-      </c>
-      <c r="X22" s="5">
-        <v>0.77290102500000002</v>
-      </c>
-      <c r="Y22" s="5">
-        <v>0.77113676900000006</v>
-      </c>
-      <c r="Z22">
-        <v>19137.5</v>
-      </c>
-      <c r="AA22">
-        <v>5.8533056999999999E-2</v>
-      </c>
-      <c r="AB22">
-        <v>20585.71429</v>
-      </c>
-      <c r="AC22">
-        <v>6.2962497000000006E-2</v>
-      </c>
-      <c r="AD22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL22" s="7" t="s">
-        <v>39</v>
+      <c r="AL22" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AQ22" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="AO22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP22" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="C23" s="12">
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>81662947.719999999</v>
       </c>
       <c r="E23">
         <v>81662947.719999999</v>
@@ -4567,16 +4288,16 @@
         <v>81662947.719999999</v>
       </c>
       <c r="G23">
-        <v>81662947.719999999</v>
+        <v>563.82868759999997</v>
       </c>
       <c r="H23">
-        <v>563.82868759999997</v>
+        <v>86.037499999999994</v>
       </c>
       <c r="I23">
-        <v>86.037499999999994</v>
+        <v>83.974999999999994</v>
       </c>
       <c r="J23">
-        <v>83.974999999999994</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -4584,14 +4305,14 @@
       <c r="L23">
         <v>0</v>
       </c>
-      <c r="M23">
-        <v>0</v>
+      <c r="M23" t="s">
+        <v>39</v>
       </c>
       <c r="N23" t="s">
-        <v>41</v>
-      </c>
-      <c r="O23" t="s">
-        <v>107</v>
+        <v>103</v>
+      </c>
+      <c r="O23" s="5">
+        <v>0</v>
       </c>
       <c r="P23" s="5">
         <v>0</v>
@@ -4599,110 +4320,309 @@
       <c r="Q23" s="5">
         <v>0</v>
       </c>
-      <c r="R23" s="5">
-        <v>0</v>
+      <c r="R23" t="s">
+        <v>35</v>
       </c>
       <c r="S23" t="s">
-        <v>37</v>
-      </c>
-      <c r="T23" t="s">
+        <v>104</v>
+      </c>
+      <c r="T23">
+        <v>48300400</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0.97499813700000004</v>
+      </c>
+      <c r="V23" s="5">
+        <v>0.96193820299999999</v>
+      </c>
+      <c r="W23" s="5">
+        <v>0.96000861299999996</v>
+      </c>
+      <c r="X23" s="5">
+        <v>0.95946203299999999</v>
+      </c>
+      <c r="Y23">
+        <v>23450</v>
+      </c>
+      <c r="Z23">
+        <v>2.4897649000000001E-2</v>
+      </c>
+      <c r="AA23">
+        <v>25857.14286</v>
+      </c>
+      <c r="AB23">
+        <v>2.7453393E-2</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE23" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK23" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO23" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="U23">
-        <v>48300400</v>
-      </c>
-      <c r="V23" s="5">
-        <v>0.97499813700000004</v>
-      </c>
-      <c r="W23" s="5">
-        <v>0.96193820299999999</v>
-      </c>
-      <c r="X23" s="5">
-        <v>0.96000861299999996</v>
-      </c>
-      <c r="Y23" s="5">
-        <v>0.95946203299999999</v>
-      </c>
-      <c r="Z23">
-        <v>23450</v>
-      </c>
-      <c r="AA23">
-        <v>2.4897649000000001E-2</v>
-      </c>
-      <c r="AB23">
-        <v>25857.14286</v>
-      </c>
-      <c r="AC23">
-        <v>2.7453393E-2</v>
-      </c>
-      <c r="AD23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL23" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AM23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP23" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ23" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="AP23" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC25" s="13"/>
+      <c r="AH25" s="13"/>
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="AC26" s="14"/>
+      <c r="AH26" s="14"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="AC27" s="14"/>
+      <c r="AH27" s="14"/>
+      <c r="AM27" s="1"/>
+      <c r="AN27" s="1"/>
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="AC28" s="14"/>
+      <c r="AH28" s="14"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="1"/>
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="AC29" s="14"/>
+      <c r="AH29" s="14"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1"/>
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="AC30" s="14"/>
+      <c r="AH30" s="14"/>
+      <c r="AM30" s="1"/>
+      <c r="AN30" s="1"/>
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="AC31" s="14"/>
+      <c r="AH31" s="14"/>
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="1"/>
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="AC32" s="14"/>
+      <c r="AH32" s="14"/>
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="1"/>
+    </row>
+    <row r="33" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="AC33" s="14"/>
+      <c r="AH33" s="14"/>
+      <c r="AM33" s="11"/>
+      <c r="AN33" s="11"/>
+    </row>
+    <row r="34" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+      <c r="X34" s="10"/>
+      <c r="AC34" s="14"/>
+      <c r="AH34" s="14"/>
+      <c r="AM34" s="8"/>
+      <c r="AN34" s="8"/>
+    </row>
+    <row r="35" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="AC35" s="14"/>
+      <c r="AH35" s="14"/>
+      <c r="AM35" s="1"/>
+      <c r="AN35" s="1"/>
+    </row>
+    <row r="36" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="AC36" s="14"/>
+      <c r="AH36" s="14"/>
+      <c r="AM36" s="1"/>
+      <c r="AN36" s="1"/>
+    </row>
+    <row r="37" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="5"/>
+      <c r="AC37" s="14"/>
+      <c r="AH37" s="14"/>
+      <c r="AM37" s="1"/>
+      <c r="AN37" s="1"/>
+    </row>
+    <row r="38" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="AC38" s="14"/>
+      <c r="AH38" s="14"/>
+      <c r="AM38" s="1"/>
+      <c r="AN38" s="1"/>
+    </row>
+    <row r="39" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="AC39" s="14"/>
+      <c r="AH39" s="14"/>
+      <c r="AM39" s="1"/>
+      <c r="AN39" s="1"/>
+    </row>
+    <row r="40" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="AC40" s="14"/>
+      <c r="AH40" s="14"/>
+      <c r="AM40" s="1"/>
+      <c r="AN40" s="1"/>
+    </row>
+    <row r="41" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="5"/>
+      <c r="AC41" s="14"/>
+      <c r="AH41" s="14"/>
+      <c r="AM41" s="1"/>
+      <c r="AN41" s="1"/>
+    </row>
+    <row r="42" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="AC42" s="14"/>
+      <c r="AH42" s="14"/>
+      <c r="AM42" s="1"/>
+      <c r="AN42" s="1"/>
+    </row>
+    <row r="43" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="5"/>
+      <c r="AC43" s="14"/>
+      <c r="AH43" s="14"/>
+      <c r="AM43" s="1"/>
+      <c r="AN43" s="1"/>
+    </row>
+    <row r="44" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="5"/>
+      <c r="X44" s="5"/>
+      <c r="AC44" s="14"/>
+      <c r="AH44" s="14"/>
+      <c r="AM44" s="1"/>
+      <c r="AN44" s="1"/>
+    </row>
+    <row r="45" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="AC45" s="14"/>
+      <c r="AH45" s="14"/>
+      <c r="AM45" s="1"/>
+      <c r="AN45" s="1"/>
+    </row>
+    <row r="46" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="AC46" s="14"/>
+      <c r="AH46" s="14"/>
+      <c r="AM46" s="1"/>
+      <c r="AN46" s="1"/>
+    </row>
+    <row r="47" spans="21:40" x14ac:dyDescent="0.25">
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+      <c r="W47" s="5"/>
+      <c r="X47" s="5"/>
+      <c r="AC47" s="14"/>
+      <c r="AH47" s="14"/>
+      <c r="AM47" s="1"/>
+      <c r="AN47" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AM2:AQ23 AJ2:AK23">
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
-      <formula>"LC"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
-      <formula>"VU"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="16" operator="equal">
-      <formula>"EN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
-      <formula>"CR"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:R23">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="O2:Q23">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4712,9 +4632,17 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:Y23">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="U2:X23">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4725,7 +4653,48 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="U26:X47">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI2:AJ23 AL2:AP23">
+    <cfRule type="cellIs" dxfId="15" priority="19" operator="equal">
+      <formula>"LC"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
+      <formula>"VU"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="21" operator="equal">
+      <formula>"EN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="22" operator="equal">
+      <formula>"CR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM25:AN47">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>"LC"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+      <formula>"VU"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+      <formula>"EN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+      <formula>"CR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4755,45 +4724,45 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" t="s">
         <v>81</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>82</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>84</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>85</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>86</v>
       </c>
-      <c r="I1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L1" t="s">
-        <v>90</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>0.120879980532887</v>
@@ -4805,10 +4774,10 @@
         <v>0.100634593016682</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H2">
         <v>0.13278348053592701</v>
@@ -4820,24 +4789,24 @@
         <v>0.117037068023323</v>
       </c>
       <c r="K2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>0.98706183119291901</v>
@@ -4849,10 +4818,10 @@
         <v>0.98706183119291901</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H3">
         <v>0.98706183119291901</v>
@@ -4864,24 +4833,24 @@
         <v>0.98706183119291901</v>
       </c>
       <c r="K3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N3" t="s">
         <v>93</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4">
         <v>0.110092469291942</v>
@@ -4893,10 +4862,10 @@
         <v>4.3144120208725101E-2</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H4">
         <v>0.131227694354518</v>
@@ -4908,24 +4877,24 @@
         <v>4.5257642714982699E-2</v>
       </c>
       <c r="K4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>0.20076611827853399</v>
@@ -4937,10 +4906,10 @@
         <v>6.0229835483560298E-2</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H5">
         <v>0.20076611827853399</v>
@@ -4952,24 +4921,24 @@
         <v>6.0229835483560298E-2</v>
       </c>
       <c r="K5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N5" t="s">
         <v>94</v>
-      </c>
-      <c r="N5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>0.43618339505369602</v>
@@ -4981,10 +4950,10 @@
         <v>0.122339275663629</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H6">
         <v>0.43927870517797202</v>
@@ -4996,24 +4965,24 @@
         <v>0.123267868700911</v>
       </c>
       <c r="K6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>1.15254384695468E-3</v>
@@ -5025,10 +4994,10 @@
         <v>3.4576315408640403E-4</v>
       </c>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H7">
         <v>1.15254384695468E-3</v>
@@ -5040,24 +5009,24 @@
         <v>3.4576315408640403E-4</v>
       </c>
       <c r="K7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0.376874012739362</v>
@@ -5069,10 +5038,10 @@
         <v>0.376874012739362</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H8">
         <v>0.376874012739362</v>
@@ -5084,24 +5053,24 @@
         <v>0.376874012739362</v>
       </c>
       <c r="K8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>0.34205787697141599</v>
@@ -5113,10 +5082,10 @@
         <v>0.27738968611314702</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H9">
         <v>0.34205787697141599</v>
@@ -5128,24 +5097,24 @@
         <v>0.27738968611314702</v>
       </c>
       <c r="K9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N9" t="s">
         <v>92</v>
-      </c>
-      <c r="L9" t="s">
-        <v>93</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="N9" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>0.99131653073036496</v>
@@ -5157,10 +5126,10 @@
         <v>0.99131653073036496</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H10">
         <v>0.99131653073036496</v>
@@ -5172,24 +5141,24 @@
         <v>0.99131653073036496</v>
       </c>
       <c r="K10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L10" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N10" t="s">
         <v>93</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N10" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <v>0.36485610996881801</v>
@@ -5201,10 +5170,10 @@
         <v>0.25354129496558198</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H11">
         <v>0.36485610996881801</v>
@@ -5216,24 +5185,24 @@
         <v>0.25354129496558198</v>
       </c>
       <c r="K11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N11" t="s">
         <v>93</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N11" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>2.8095486074266599E-2</v>
@@ -5245,10 +5214,10 @@
         <v>1.40477430371333E-2</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H12">
         <v>2.8095486074266599E-2</v>
@@ -5260,24 +5229,24 @@
         <v>1.40477430371333E-2</v>
       </c>
       <c r="K12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <v>0.124348146510028</v>
@@ -5289,10 +5258,10 @@
         <v>0.111169571256719</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H13">
         <v>0.124348146510028</v>
@@ -5304,24 +5273,24 @@
         <v>0.11598546160994699</v>
       </c>
       <c r="K13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>0.10119077074242799</v>
@@ -5333,10 +5302,10 @@
         <v>6.5197936490554803E-2</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H14">
         <v>0.12632102418622701</v>
@@ -5348,24 +5317,24 @@
         <v>6.6968239964264195E-2</v>
       </c>
       <c r="K14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C15">
         <v>0.81360744871954205</v>
@@ -5377,10 +5346,10 @@
         <v>0.81360744871954205</v>
       </c>
       <c r="F15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H15">
         <v>0.81360744871954205</v>
@@ -5392,24 +5361,24 @@
         <v>0.81360744871954205</v>
       </c>
       <c r="K15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16">
         <v>0.242452582558109</v>
@@ -5421,10 +5390,10 @@
         <v>0.236838003342252</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H16">
         <v>0.24248031033075401</v>
@@ -5436,24 +5405,24 @@
         <v>0.230317721114628</v>
       </c>
       <c r="K16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N16" t="s">
         <v>92</v>
-      </c>
-      <c r="N16" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -5465,10 +5434,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -5480,24 +5449,24 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C18">
         <v>0.76070900634694505</v>
@@ -5509,10 +5478,10 @@
         <v>0.22821270190408299</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H18">
         <v>0.77047231596424504</v>
@@ -5524,24 +5493,24 @@
         <v>0.23114169478927399</v>
       </c>
       <c r="K18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>0.39079534235927998</v>
@@ -5553,10 +5522,10 @@
         <v>0.13350206375425899</v>
       </c>
       <c r="F19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H19">
         <v>0.45884258395043198</v>
@@ -5568,24 +5537,24 @@
         <v>0.14277376586374599</v>
       </c>
       <c r="K19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N19" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C20">
         <v>5.9571307971852401E-2</v>
@@ -5597,10 +5566,10 @@
         <v>4.6357562761259401E-2</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H20">
         <v>6.5144493821399696E-2</v>
@@ -5612,24 +5581,24 @@
         <v>5.1235268516842201E-2</v>
       </c>
       <c r="K20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C21">
         <v>0.21221775304646301</v>
@@ -5641,10 +5610,10 @@
         <v>0.20416495473558199</v>
       </c>
       <c r="F21" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H21">
         <v>0.23649906499637299</v>
@@ -5656,24 +5625,24 @@
         <v>0.16145246445202299</v>
       </c>
       <c r="K21" t="s">
+        <v>89</v>
+      </c>
+      <c r="L21" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N21" t="s">
         <v>93</v>
-      </c>
-      <c r="L21" t="s">
-        <v>93</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N21" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C22">
         <v>0.23243861000832999</v>
@@ -5685,10 +5654,10 @@
         <v>0.20384078728485999</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H22">
         <v>0.239431121502303</v>
@@ -5700,24 +5669,24 @@
         <v>0.20244072895218401</v>
       </c>
       <c r="K22" t="s">
+        <v>89</v>
+      </c>
+      <c r="L22" t="s">
+        <v>89</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N22" t="s">
         <v>93</v>
-      </c>
-      <c r="L22" t="s">
-        <v>93</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N22" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C23">
         <v>0.92019794709416902</v>
@@ -5729,10 +5698,10 @@
         <v>0.92019794709416902</v>
       </c>
       <c r="F23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H23">
         <v>0.92019794709416902</v>
@@ -5744,44 +5713,44 @@
         <v>0.92019794709416902</v>
       </c>
       <c r="K23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s">
+        <v>89</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N23" t="s">
         <v>93</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N23" t="s">
-        <v>97</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:L23 G2:G23">
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+  <conditionalFormatting sqref="G2:G23">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"NP"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"PP"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"MP"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"WP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:N23">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+  <conditionalFormatting sqref="L2:N23">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"NP"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"PP"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"MP"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"WP"</formula>
     </cfRule>
   </conditionalFormatting>
